--- a/Team-Data/2013-14/4-2-2013-14.xlsx
+++ b/Team-Data/2013-14/4-2-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E2" t="n">
         <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>0.432</v>
+        <v>0.438</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
@@ -679,13 +746,13 @@
         <v>37.2</v>
       </c>
       <c r="J2" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="K2" t="n">
         <v>0.454</v>
       </c>
       <c r="L2" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M2" t="n">
         <v>25.8</v>
@@ -694,10 +761,10 @@
         <v>0.366</v>
       </c>
       <c r="O2" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q2" t="n">
         <v>0.78</v>
@@ -712,7 +779,7 @@
         <v>40</v>
       </c>
       <c r="U2" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="V2" t="n">
         <v>15.4</v>
@@ -727,28 +794,28 @@
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA2" t="n">
         <v>19.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>100.9</v>
+        <v>101</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.4</v>
+        <v>-1.2</v>
       </c>
       <c r="AD2" t="n">
         <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF2" t="n">
         <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH2" t="n">
         <v>11</v>
@@ -757,7 +824,7 @@
         <v>18</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
         <v>13</v>
@@ -769,16 +836,16 @@
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO2" t="n">
         <v>17</v>
       </c>
       <c r="AP2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
         <v>28</v>
@@ -811,10 +878,10 @@
         <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E3" t="n">
         <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>0.307</v>
+        <v>0.311</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J3" t="n">
         <v>83.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0.432</v>
+        <v>0.433</v>
       </c>
       <c r="L3" t="n">
         <v>6.7</v>
@@ -873,25 +940,25 @@
         <v>20.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.327</v>
+        <v>0.33</v>
       </c>
       <c r="O3" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="R3" t="n">
         <v>12</v>
       </c>
       <c r="S3" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
         <v>20.7</v>
@@ -900,7 +967,7 @@
         <v>15.3</v>
       </c>
       <c r="W3" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X3" t="n">
         <v>4.3</v>
@@ -912,16 +979,16 @@
         <v>21.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB3" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>-4.5</v>
+        <v>-4.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE3" t="n">
         <v>26</v>
@@ -936,7 +1003,7 @@
         <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ3" t="n">
         <v>10</v>
@@ -954,7 +1021,7 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
         <v>27</v>
@@ -972,10 +1039,10 @@
         <v>16</v>
       </c>
       <c r="AU3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW3" t="n">
         <v>23</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E4" t="n">
         <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>0.541</v>
+        <v>0.548</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J4" t="n">
-        <v>78.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L4" t="n">
         <v>8.6</v>
@@ -1055,13 +1122,13 @@
         <v>23.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O4" t="n">
         <v>18.6</v>
       </c>
       <c r="P4" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0.759</v>
@@ -1070,16 +1137,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="T4" t="n">
-        <v>38.2</v>
+        <v>38.5</v>
       </c>
       <c r="U4" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V4" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W4" t="n">
         <v>8.6</v>
@@ -1091,16 +1158,16 @@
         <v>4.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>98.5</v>
+        <v>98.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="AD4" t="n">
         <v>25</v>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1154,16 +1221,16 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY4" t="n">
         <v>9</v>
@@ -1172,13 +1239,13 @@
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -1207,58 +1274,58 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5" t="n">
         <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>0.493</v>
+        <v>0.486</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J5" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K5" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L5" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M5" t="n">
         <v>17.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.352</v>
+        <v>0.349</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P5" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="R5" t="n">
         <v>9.4</v>
       </c>
       <c r="S5" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T5" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U5" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V5" t="n">
         <v>12.3</v>
@@ -1267,7 +1334,7 @@
         <v>6.1</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y5" t="n">
         <v>5.1</v>
@@ -1279,13 +1346,13 @@
         <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.8</v>
+        <v>96.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1300,7 +1367,7 @@
         <v>13</v>
       </c>
       <c r="AI5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ5" t="n">
         <v>22</v>
@@ -1309,16 +1376,16 @@
         <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM5" t="n">
         <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
         <v>11</v>
@@ -1330,10 +1397,10 @@
         <v>25</v>
       </c>
       <c r="AS5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU5" t="n">
         <v>17</v>
@@ -1348,7 +1415,7 @@
         <v>9</v>
       </c>
       <c r="AY5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
         <v>2</v>
@@ -1360,7 +1427,7 @@
         <v>25</v>
       </c>
       <c r="BC5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -1389,85 +1456,85 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.573</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="J6" t="n">
         <v>80.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L6" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.347</v>
+        <v>0.344</v>
       </c>
       <c r="O6" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R6" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S6" t="n">
         <v>32.9</v>
       </c>
       <c r="T6" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="U6" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V6" t="n">
         <v>15.2</v>
       </c>
       <c r="W6" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z6" t="n">
         <v>19.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1491,7 +1558,7 @@
         <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM6" t="n">
         <v>28</v>
@@ -1500,10 +1567,10 @@
         <v>25</v>
       </c>
       <c r="AO6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
         <v>9</v>
@@ -1512,10 +1579,10 @@
         <v>10</v>
       </c>
       <c r="AS6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT6" t="n">
         <v>9</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>10</v>
       </c>
       <c r="AU6" t="n">
         <v>11</v>
@@ -1524,13 +1591,13 @@
         <v>19</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
       </c>
       <c r="AY6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ6" t="n">
         <v>4</v>
@@ -1542,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1638,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
         <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>0.408</v>
+        <v>0.4</v>
       </c>
       <c r="H7" t="n">
         <v>48.6</v>
       </c>
       <c r="I7" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J7" t="n">
-        <v>84.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0.435</v>
+        <v>0.433</v>
       </c>
       <c r="L7" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M7" t="n">
         <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="O7" t="n">
         <v>17</v>
@@ -1610,7 +1677,7 @@
         <v>22.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R7" t="n">
         <v>12.1</v>
@@ -1619,10 +1686,10 @@
         <v>32</v>
       </c>
       <c r="T7" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V7" t="n">
         <v>14.4</v>
@@ -1637,19 +1704,19 @@
         <v>5.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
         <v>19.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>97.5</v>
+        <v>97.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.8</v>
+        <v>-4.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
@@ -1670,7 +1737,7 @@
         <v>9</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
         <v>18</v>
@@ -1694,13 +1761,13 @@
         <v>6</v>
       </c>
       <c r="AS7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT7" t="n">
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -1831,25 +1898,25 @@
         <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1858,7 +1925,7 @@
         <v>8</v>
       </c>
       <c r="AM8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN8" t="n">
         <v>3</v>
@@ -1891,10 +1958,10 @@
         <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ8" t="n">
         <v>11</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -1935,37 +2002,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n">
         <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>0.44</v>
+        <v>0.432</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>38.3</v>
+        <v>38.1</v>
       </c>
       <c r="J9" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.449</v>
+        <v>0.447</v>
       </c>
       <c r="L9" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M9" t="n">
         <v>23.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.362</v>
+        <v>0.359</v>
       </c>
       <c r="O9" t="n">
         <v>19</v>
@@ -1977,25 +2044,25 @@
         <v>0.718</v>
       </c>
       <c r="R9" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S9" t="n">
         <v>33</v>
       </c>
       <c r="T9" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U9" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V9" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W9" t="n">
         <v>7.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y9" t="n">
         <v>5.6</v>
@@ -2007,37 +2074,37 @@
         <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>104</v>
+        <v>103.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.2</v>
+        <v>-2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ9" t="n">
         <v>5</v>
       </c>
       <c r="AK9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
@@ -2061,25 +2128,25 @@
         <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW9" t="n">
         <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
         <v>25</v>
       </c>
       <c r="AZ9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA9" t="n">
         <v>7</v>
@@ -2088,7 +2155,7 @@
         <v>9</v>
       </c>
       <c r="BC9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E10" t="n">
         <v>27</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2135,10 +2202,10 @@
         <v>38.9</v>
       </c>
       <c r="J10" t="n">
-        <v>87</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L10" t="n">
         <v>6.1</v>
@@ -2147,13 +2214,13 @@
         <v>19.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.319</v>
+        <v>0.318</v>
       </c>
       <c r="O10" t="n">
         <v>16.8</v>
       </c>
       <c r="P10" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q10" t="n">
         <v>0.669</v>
@@ -2168,13 +2235,13 @@
         <v>45.2</v>
       </c>
       <c r="U10" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V10" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W10" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X10" t="n">
         <v>5</v>
@@ -2183,7 +2250,7 @@
         <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA10" t="n">
         <v>20.4</v>
@@ -2192,10 +2259,10 @@
         <v>100.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2216,10 +2283,10 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM10" t="n">
         <v>24</v>
@@ -2243,13 +2310,13 @@
         <v>21</v>
       </c>
       <c r="AT10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
         <v>7</v>
@@ -2261,13 +2328,13 @@
         <v>17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BB10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BC10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E11" t="n">
         <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G11" t="n">
-        <v>0.613</v>
+        <v>0.622</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J11" t="n">
         <v>84.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L11" t="n">
         <v>9.199999999999999</v>
@@ -2332,28 +2399,28 @@
         <v>0.376</v>
       </c>
       <c r="O11" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P11" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.754</v>
+        <v>0.752</v>
       </c>
       <c r="R11" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="T11" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V11" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W11" t="n">
         <v>7.6</v>
@@ -2368,16 +2435,16 @@
         <v>21.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.2</v>
+        <v>103.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2404,13 +2471,13 @@
         <v>6</v>
       </c>
       <c r="AM11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN11" t="n">
         <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
         <v>24</v>
@@ -2422,10 +2489,10 @@
         <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
         <v>9</v>
@@ -2446,13 +2513,13 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB11" t="n">
         <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -2481,28 +2548,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E12" t="n">
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>0.662</v>
+        <v>0.671</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J12" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L12" t="n">
         <v>9.300000000000001</v>
@@ -2532,7 +2599,7 @@
         <v>45.1</v>
       </c>
       <c r="U12" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V12" t="n">
         <v>16.4</v>
@@ -2541,13 +2608,13 @@
         <v>7.5</v>
       </c>
       <c r="X12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA12" t="n">
         <v>24.5</v>
@@ -2556,7 +2623,7 @@
         <v>106.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AD12" t="n">
         <v>25</v>
@@ -2571,10 +2638,10 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
@@ -2607,16 +2674,16 @@
         <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2625,7 +2692,7 @@
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
         <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.697</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J13" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L13" t="n">
         <v>6.6</v>
@@ -2693,7 +2760,7 @@
         <v>18.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O13" t="n">
         <v>18.3</v>
@@ -2702,25 +2769,25 @@
         <v>23.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="R13" t="n">
         <v>10.2</v>
       </c>
       <c r="S13" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="T13" t="n">
         <v>45</v>
       </c>
       <c r="U13" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V13" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W13" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X13" t="n">
         <v>5.6</v>
@@ -2732,16 +2799,16 @@
         <v>20.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB13" t="n">
         <v>96.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
@@ -2756,7 +2823,7 @@
         <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ13" t="n">
         <v>26</v>
@@ -2771,10 +2838,10 @@
         <v>25</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
         <v>14</v>
@@ -2792,7 +2859,7 @@
         <v>7</v>
       </c>
       <c r="AU13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV13" t="n">
         <v>20</v>
@@ -2801,16 +2868,16 @@
         <v>26</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY13" t="n">
         <v>15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -2845,37 +2912,37 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
         <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>0.711</v>
+        <v>0.707</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J14" t="n">
         <v>82.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.474</v>
+        <v>0.475</v>
       </c>
       <c r="L14" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M14" t="n">
         <v>23.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="O14" t="n">
         <v>21.1</v>
@@ -2884,16 +2951,16 @@
         <v>28.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.732</v>
+        <v>0.729</v>
       </c>
       <c r="R14" t="n">
         <v>10.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T14" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U14" t="n">
         <v>24.5</v>
@@ -2917,16 +2984,16 @@
         <v>23.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.7</v>
+        <v>107.6</v>
       </c>
       <c r="AC14" t="n">
         <v>7.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>3</v>
@@ -2938,7 +3005,7 @@
         <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AJ14" t="n">
         <v>20</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2968,7 +3035,7 @@
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>15</v>
@@ -2980,7 +3047,7 @@
         <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="n">
         <v>13</v>
@@ -2992,7 +3059,7 @@
         <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E15" t="n">
         <v>25</v>
       </c>
       <c r="F15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,16 +3112,16 @@
         <v>38.2</v>
       </c>
       <c r="J15" t="n">
-        <v>85</v>
+        <v>84.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L15" t="n">
         <v>9.4</v>
       </c>
       <c r="M15" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="N15" t="n">
         <v>0.384</v>
@@ -3063,22 +3130,22 @@
         <v>16.9</v>
       </c>
       <c r="P15" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R15" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T15" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U15" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="V15" t="n">
         <v>15.3</v>
@@ -3105,7 +3172,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3120,19 +3187,19 @@
         <v>30</v>
       </c>
       <c r="AI15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ15" t="n">
         <v>6</v>
       </c>
       <c r="AK15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL15" t="n">
         <v>4</v>
       </c>
       <c r="AM15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN15" t="n">
         <v>4</v>
@@ -3150,22 +3217,22 @@
         <v>26</v>
       </c>
       <c r="AS15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU15" t="n">
         <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW15" t="n">
         <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
         <v>13</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" t="n">
         <v>44</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>0.587</v>
+        <v>0.595</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J16" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K16" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L16" t="n">
         <v>4.9</v>
@@ -3242,10 +3309,10 @@
         <v>0.353</v>
       </c>
       <c r="O16" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="P16" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0.742</v>
@@ -3254,7 +3321,7 @@
         <v>11.5</v>
       </c>
       <c r="S16" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T16" t="n">
         <v>42.3</v>
@@ -3263,7 +3330,7 @@
         <v>21.7</v>
       </c>
       <c r="V16" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="W16" t="n">
         <v>7.7</v>
@@ -3275,19 +3342,19 @@
         <v>5.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE16" t="n">
         <v>9</v>
@@ -3302,10 +3369,10 @@
         <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3323,19 +3390,19 @@
         <v>30</v>
       </c>
       <c r="AP16" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AQ16" t="n">
         <v>23</v>
       </c>
       <c r="AR16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS16" t="n">
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
@@ -3347,10 +3414,10 @@
         <v>13</v>
       </c>
       <c r="AX16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ16" t="n">
         <v>6</v>
@@ -3362,7 +3429,7 @@
         <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F17" t="n">
         <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>0.703</v>
+        <v>0.699</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
@@ -3418,19 +3485,19 @@
         <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="N17" t="n">
         <v>0.365</v>
       </c>
       <c r="O17" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P17" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R17" t="n">
         <v>7.6</v>
@@ -3445,7 +3512,7 @@
         <v>22.9</v>
       </c>
       <c r="V17" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W17" t="n">
         <v>8.9</v>
@@ -3457,16 +3524,16 @@
         <v>3</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>102.8</v>
+        <v>102.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AD17" t="n">
         <v>25</v>
@@ -3505,7 +3572,7 @@
         <v>15</v>
       </c>
       <c r="AP17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3514,7 +3581,7 @@
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3523,13 +3590,13 @@
         <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
         <v>2</v>
       </c>
       <c r="AX17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3538,7 +3605,7 @@
         <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
         <v>11</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E18" t="n">
         <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
-        <v>0.187</v>
+        <v>0.189</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3591,7 +3658,7 @@
         <v>35.9</v>
       </c>
       <c r="J18" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K18" t="n">
         <v>0.434</v>
@@ -3603,16 +3670,16 @@
         <v>19.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O18" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P18" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.751</v>
+        <v>0.75</v>
       </c>
       <c r="R18" t="n">
         <v>11.9</v>
@@ -3624,10 +3691,10 @@
         <v>41.2</v>
       </c>
       <c r="U18" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V18" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W18" t="n">
         <v>6.7</v>
@@ -3639,19 +3706,19 @@
         <v>5.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3666,40 +3733,40 @@
         <v>7</v>
       </c>
       <c r="AI18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ18" t="n">
         <v>15</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL18" t="n">
         <v>20</v>
       </c>
       <c r="AM18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP18" t="n">
         <v>20</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>21</v>
       </c>
       <c r="AQ18" t="n">
         <v>20</v>
       </c>
       <c r="AR18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU18" t="n">
         <v>16</v>
@@ -3720,7 +3787,7 @@
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BB18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -3755,46 +3822,46 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F19" t="n">
         <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.493</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="J19" t="n">
-        <v>87.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L19" t="n">
         <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="N19" t="n">
         <v>0.344</v>
       </c>
       <c r="O19" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="P19" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="R19" t="n">
         <v>12.5</v>
@@ -3806,7 +3873,7 @@
         <v>44.9</v>
       </c>
       <c r="U19" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V19" t="n">
         <v>13.8</v>
@@ -3815,22 +3882,22 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.6</v>
+        <v>106.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
         <v>25</v>
@@ -3854,7 +3921,7 @@
         <v>2</v>
       </c>
       <c r="AK19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
         <v>17</v>
@@ -3872,13 +3939,13 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
         <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
@@ -3902,13 +3969,13 @@
         <v>3</v>
       </c>
       <c r="BA19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB19" t="n">
         <v>4</v>
       </c>
       <c r="BC19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E20" t="n">
         <v>32</v>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>0.427</v>
+        <v>0.432</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
@@ -3955,31 +4022,31 @@
         <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>0.46</v>
       </c>
       <c r="L20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M20" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O20" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="P20" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="Q20" t="n">
         <v>0.771</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S20" t="n">
         <v>30.4</v>
@@ -3994,37 +4061,37 @@
         <v>13.9</v>
       </c>
       <c r="W20" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X20" t="n">
         <v>6.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
         <v>22.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.6</v>
+        <v>-2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH20" t="n">
         <v>8</v>
@@ -4033,7 +4100,7 @@
         <v>14</v>
       </c>
       <c r="AJ20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK20" t="n">
         <v>9</v>
@@ -4045,19 +4112,19 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ20" t="n">
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
@@ -4078,19 +4145,19 @@
         <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ20" t="n">
         <v>27</v>
       </c>
       <c r="BA20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB20" t="n">
         <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -4119,37 +4186,37 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E21" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F21" t="n">
         <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>0.434</v>
+        <v>0.427</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J21" t="n">
-        <v>82.5</v>
+        <v>82.7</v>
       </c>
       <c r="K21" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M21" t="n">
         <v>24.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O21" t="n">
         <v>15.2</v>
@@ -4173,40 +4240,40 @@
         <v>20.3</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W21" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X21" t="n">
         <v>4.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>98.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.1</v>
+        <v>-1.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
         <v>18</v>
       </c>
       <c r="AF21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
         <v>10</v>
@@ -4215,10 +4282,10 @@
         <v>19</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK21" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AL21" t="n">
         <v>7</v>
@@ -4227,13 +4294,13 @@
         <v>5</v>
       </c>
       <c r="AN21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
       </c>
       <c r="AP21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ21" t="n">
         <v>17</v>
@@ -4260,7 +4327,7 @@
         <v>19</v>
       </c>
       <c r="AY21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ21" t="n">
         <v>23</v>
@@ -4269,10 +4336,10 @@
         <v>24</v>
       </c>
       <c r="BB21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4394,10 +4461,10 @@
         <v>16</v>
       </c>
       <c r="AI22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK22" t="n">
         <v>6</v>
@@ -4409,13 +4476,13 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -4424,7 +4491,7 @@
         <v>19</v>
       </c>
       <c r="AS22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
         <v>5</v>
@@ -4433,7 +4500,7 @@
         <v>13</v>
       </c>
       <c r="AV22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW22" t="n">
         <v>10</v>
@@ -4448,7 +4515,7 @@
         <v>26</v>
       </c>
       <c r="BA22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
         <v>5</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -4483,22 +4550,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E23" t="n">
         <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G23" t="n">
-        <v>0.28</v>
+        <v>0.284</v>
       </c>
       <c r="H23" t="n">
         <v>48.7</v>
       </c>
       <c r="I23" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J23" t="n">
         <v>83.2</v>
@@ -4507,13 +4574,13 @@
         <v>0.444</v>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O23" t="n">
         <v>16.1</v>
@@ -4522,16 +4589,16 @@
         <v>21</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R23" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T23" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U23" t="n">
         <v>21</v>
@@ -4552,16 +4619,16 @@
         <v>20.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4582,13 +4649,13 @@
         <v>13</v>
       </c>
       <c r="AK23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="n">
         <v>21</v>
       </c>
       <c r="AM23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN23" t="n">
         <v>23</v>
@@ -4606,7 +4673,7 @@
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
         <v>18</v>
@@ -4615,10 +4682,10 @@
         <v>22</v>
       </c>
       <c r="AV23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E24" t="n">
         <v>16</v>
       </c>
       <c r="F24" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G24" t="n">
-        <v>0.213</v>
+        <v>0.216</v>
       </c>
       <c r="H24" t="n">
         <v>48.5</v>
@@ -4692,10 +4759,10 @@
         <v>7.1</v>
       </c>
       <c r="M24" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.31</v>
+        <v>0.311</v>
       </c>
       <c r="O24" t="n">
         <v>16.4</v>
@@ -4710,40 +4777,40 @@
         <v>11.9</v>
       </c>
       <c r="S24" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T24" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="U24" t="n">
         <v>21.9</v>
       </c>
       <c r="V24" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="W24" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="Z24" t="n">
         <v>22.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="AC24" t="n">
-        <v>-11.2</v>
+        <v>-11</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4770,28 +4837,28 @@
         <v>19</v>
       </c>
       <c r="AM24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN24" t="n">
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E25" t="n">
         <v>44</v>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" t="n">
-        <v>0.587</v>
+        <v>0.595</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4865,7 +4932,7 @@
         <v>38.6</v>
       </c>
       <c r="J25" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K25" t="n">
         <v>0.462</v>
@@ -4874,37 +4941,37 @@
         <v>9.5</v>
       </c>
       <c r="M25" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O25" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P25" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R25" t="n">
         <v>11.4</v>
       </c>
       <c r="S25" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T25" t="n">
         <v>43.2</v>
       </c>
       <c r="U25" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="V25" t="n">
         <v>15.5</v>
       </c>
       <c r="W25" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X25" t="n">
         <v>4.6</v>
@@ -4925,7 +4992,7 @@
         <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -4940,10 +5007,10 @@
         <v>24</v>
       </c>
       <c r="AI25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>11</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>12</v>
       </c>
       <c r="AK25" t="n">
         <v>8</v>
@@ -4955,7 +5022,7 @@
         <v>4</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>9</v>
@@ -4967,7 +5034,7 @@
         <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
@@ -4979,13 +5046,13 @@
         <v>29</v>
       </c>
       <c r="AV25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW25" t="n">
         <v>9</v>
       </c>
       <c r="AX25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY25" t="n">
         <v>7</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -5122,13 +5189,13 @@
         <v>15</v>
       </c>
       <c r="AI26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ26" t="n">
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
         <v>1</v>
@@ -5137,13 +5204,13 @@
         <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>7</v>
       </c>
       <c r="AP26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5158,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="AU26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
@@ -5176,13 +5243,13 @@
         <v>7</v>
       </c>
       <c r="BA26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB26" t="n">
         <v>2</v>
       </c>
       <c r="BC26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F27" t="n">
         <v>48</v>
       </c>
       <c r="G27" t="n">
-        <v>0.36</v>
+        <v>0.351</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J27" t="n">
         <v>82.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L27" t="n">
         <v>6.2</v>
@@ -5244,28 +5311,28 @@
         <v>0.336</v>
       </c>
       <c r="O27" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="P27" t="n">
         <v>27.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="R27" t="n">
         <v>12.2</v>
       </c>
       <c r="S27" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T27" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="U27" t="n">
         <v>18.9</v>
       </c>
       <c r="V27" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W27" t="n">
         <v>7.2</v>
@@ -5277,28 +5344,28 @@
         <v>5.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.1</v>
+        <v>101</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
         <v>13</v>
@@ -5307,13 +5374,13 @@
         <v>20</v>
       </c>
       <c r="AJ27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK27" t="n">
         <v>16</v>
       </c>
       <c r="AL27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM27" t="n">
         <v>26</v>
@@ -5337,25 +5404,25 @@
         <v>13</v>
       </c>
       <c r="AT27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY27" t="n">
         <v>26</v>
       </c>
       <c r="AZ27" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BA27" t="n">
         <v>4</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E28" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.787</v>
+        <v>0.784</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
@@ -5414,16 +5481,16 @@
         <v>83</v>
       </c>
       <c r="K28" t="n">
-        <v>0.49</v>
+        <v>0.489</v>
       </c>
       <c r="L28" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M28" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.399</v>
+        <v>0.402</v>
       </c>
       <c r="O28" t="n">
         <v>15.9</v>
@@ -5432,7 +5499,7 @@
         <v>20.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.785</v>
+        <v>0.784</v>
       </c>
       <c r="R28" t="n">
         <v>9.199999999999999</v>
@@ -5453,13 +5520,13 @@
         <v>7.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AA28" t="n">
         <v>19.5</v>
@@ -5468,10 +5535,10 @@
         <v>105.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5495,7 +5562,7 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>17</v>
@@ -5513,13 +5580,13 @@
         <v>4</v>
       </c>
       <c r="AR28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS28" t="n">
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5528,7 +5595,7 @@
         <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E29" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F29" t="n">
         <v>32</v>
       </c>
       <c r="G29" t="n">
-        <v>0.573</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>48.7</v>
       </c>
       <c r="I29" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J29" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K29" t="n">
         <v>0.444</v>
@@ -5608,25 +5675,25 @@
         <v>0.366</v>
       </c>
       <c r="O29" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="P29" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.782</v>
+        <v>0.783</v>
       </c>
       <c r="R29" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S29" t="n">
         <v>31.2</v>
       </c>
       <c r="T29" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U29" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V29" t="n">
         <v>14.2</v>
@@ -5638,22 +5705,22 @@
         <v>4.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.8</v>
+        <v>100.7</v>
       </c>
       <c r="AC29" t="n">
         <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5677,25 +5744,25 @@
         <v>22</v>
       </c>
       <c r="AL29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM29" t="n">
         <v>11</v>
       </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO29" t="n">
         <v>6</v>
       </c>
       <c r="AP29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ29" t="n">
         <v>6</v>
       </c>
       <c r="AR29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS29" t="n">
         <v>19</v>
@@ -5704,13 +5771,13 @@
         <v>17</v>
       </c>
       <c r="AU29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX29" t="n">
         <v>23</v>
@@ -5722,13 +5789,13 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB29" t="n">
         <v>16</v>
       </c>
       <c r="BC29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -5835,19 +5902,19 @@
         <v>-7</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>26</v>
       </c>
       <c r="AF30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH30" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI30" t="n">
         <v>29</v>
@@ -5868,7 +5935,7 @@
         <v>22</v>
       </c>
       <c r="AO30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP30" t="n">
         <v>22</v>
@@ -5886,10 +5953,10 @@
         <v>25</v>
       </c>
       <c r="AU30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW30" t="n">
         <v>27</v>
@@ -5898,13 +5965,13 @@
         <v>20</v>
       </c>
       <c r="AY30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ30" t="n">
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E31" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F31" t="n">
         <v>36</v>
       </c>
       <c r="G31" t="n">
-        <v>0.52</v>
+        <v>0.514</v>
       </c>
       <c r="H31" t="n">
         <v>48.9</v>
       </c>
       <c r="I31" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J31" t="n">
-        <v>84.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.457</v>
+        <v>0.455</v>
       </c>
       <c r="L31" t="n">
         <v>8.1</v>
@@ -5969,7 +6036,7 @@
         <v>20.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0.388</v>
+        <v>0.387</v>
       </c>
       <c r="O31" t="n">
         <v>15.5</v>
@@ -5978,22 +6045,22 @@
         <v>21.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.735</v>
+        <v>0.733</v>
       </c>
       <c r="R31" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S31" t="n">
         <v>31.4</v>
       </c>
       <c r="T31" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U31" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V31" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W31" t="n">
         <v>8.300000000000001</v>
@@ -6002,7 +6069,7 @@
         <v>4.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z31" t="n">
         <v>20.6</v>
@@ -6011,13 +6078,13 @@
         <v>19.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.9</v>
+        <v>100.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6032,13 +6099,13 @@
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ31" t="n">
         <v>8</v>
       </c>
       <c r="AK31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL31" t="n">
         <v>15</v>
@@ -6062,16 +6129,16 @@
         <v>17</v>
       </c>
       <c r="AS31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT31" t="n">
         <v>19</v>
       </c>
       <c r="AU31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW31" t="n">
         <v>11</v>
@@ -6086,10 +6153,10 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BC31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-2-2013-14</t>
+          <t>2014-04-02</t>
         </is>
       </c>
     </row>
